--- a/app/reports/ORCL_research.xlsx
+++ b/app/reports/ORCL_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.578</v>
+        <v>0.583</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>126.41</v>
+        <v>122.91</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.333</v>
+        <v>0.348</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04604000091552735</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>2880471027.039</v>
+        <v>2880471159.97071</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>126.41</v>
+        <v>122.91</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>364120342528</v>
+        <v>354038710272</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>21.68</v>
+        <v>21.08</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>16.57</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>94306877440</v>
+        <v>93472120832</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.564895</v>
+        <v>13.444825</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.843</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>671245467648</v>
+        <v>667686797312</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>60.240604</v>
+        <v>59.92123</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>2764.288</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>118403309568</v>
+        <v>120176246784</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>62.397686</v>
+        <v>63.332012</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>48.986</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>20235216</v>
+        <v>17385344</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>578461632</v>
+        <v>575947840</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>188.27272</v>
+        <v>187.45456</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>26.261</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>317356179456</v>
+        <v>325809111040</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>148.74158</v>
+        <v>152.70338</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>153.424</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>1274678656</v>
+        <v>1278886784</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>68.84090999999999</v>
+        <v>69.068184</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>47.542</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>187497398272</v>
+        <v>188027928576</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>22.368494</v>
+        <v>22.431787</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>15.795</v>

--- a/app/reports/ORCL_research.xlsx
+++ b/app/reports/ORCL_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.583</v>
+        <v>0.579</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>122.91</v>
+        <v>125.59</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.348</v>
+        <v>0.336</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04625999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>2880471159.97071</v>
+        <v>2880471053.045625</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>122.91</v>
+        <v>125.59</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>354038710272</v>
+        <v>361758359552</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>21.08</v>
+        <v>21.54</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>16.57</v>
+        <v>16.09</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>93472120832</v>
+        <v>89890652160</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>13.444825</v>
+        <v>12.929674</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.843</v>
+        <v>9.74</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>3.8</v>
+        <v>3.761</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>667686797312</v>
+        <v>697256771584</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>59.92123</v>
+        <v>62.87842</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>2764.288</v>
+        <v>2750.746</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1055.433</v>
+        <v>1050.263</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>120176246784</v>
+        <v>114952683520</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>63.332012</v>
+        <v>60.814037</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>48.986</v>
+        <v>48.598</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>16.271</v>
+        <v>16.142</v>
       </c>
     </row>
     <row r="9">
@@ -1604,12 +1604,12 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>17385344</v>
+        <v>17758048</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n">
-        <v>0.717</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="10">
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>575947840</v>
+        <v>576227136</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>187.45456</v>
+        <v>187.54544</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>26.261</v>
+        <v>26.396</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.062</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="11">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>325809111040</v>
+        <v>318482907136</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>152.70338</v>
+        <v>149.26967</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>153.424</v>
+        <v>156.358</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>59.272</v>
+        <v>60.406</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>1278886784</v>
+        <v>1256372608</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>69.068184</v>
+        <v>67.85227</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>47.542</v>
+        <v>47.782</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>3.56</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>188027928576</v>
+        <v>182651977728</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>22.431787</v>
+        <v>21.790434</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>15.795</v>
+        <v>15.726</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>4.908</v>
+        <v>4.887</v>
       </c>
     </row>
     <row r="15">
